--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_TARGIB WATTAHRIB.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_TARGIB WATTAHRIB.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
